--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_28_R3.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_28_R3.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>K. PUNTER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9854</v>
+        <v>8.6654</v>
       </c>
       <c r="E2" t="n">
-        <v>7.329</v>
+        <v>7.6011</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6564</v>
+        <v>1.0643</v>
       </c>
       <c r="G2" t="n">
-        <v>4.2656</v>
+        <v>5.7461</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6025</v>
+        <v>4.4413</v>
       </c>
       <c r="I2" t="n">
-        <v>1.663</v>
+        <v>1.3049</v>
       </c>
       <c r="J2" t="n">
-        <v>6.06</v>
+        <v>7.2045</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8651</v>
+        <v>5.3678</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1949</v>
+        <v>1.8367</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7944</v>
+        <v>-1.4583</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2626</v>
+        <v>-0.9265</v>
       </c>
       <c r="O2" t="n">
         <v>-0.5319</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7921</v>
+        <v>0.2388</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1968</v>
+        <v>0.0356</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5953000000000001</v>
+        <v>0.2032</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. PUNTER</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9851</v>
+        <v>7.8174</v>
       </c>
       <c r="E3" t="n">
-        <v>7.2905</v>
+        <v>7.329</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6947</v>
+        <v>0.4884</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7461</v>
+        <v>4.2656</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4413</v>
+        <v>2.6025</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3049</v>
+        <v>1.663</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2045</v>
+        <v>6.06</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3678</v>
+        <v>3.8651</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8367</v>
+        <v>2.1949</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4583</v>
+        <v>-1.7944</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9265</v>
+        <v>-1.2626</v>
       </c>
       <c r="O3" t="n">
         <v>-0.5319</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4415</v>
+        <v>0.624</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.275</v>
+        <v>0.1968</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1665</v>
+        <v>0.4272</v>
       </c>
       <c r="V3" t="n">
-        <v>2.6805</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6805</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>W. CLYBURN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9701</v>
+        <v>2.2574</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0772</v>
+        <v>3.3238</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1071</v>
+        <v>-1.0664</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0327</v>
+        <v>1.1823</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0577</v>
+        <v>-0.6145</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09039999999999999</v>
+        <v>1.7968</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4986</v>
+        <v>3.8917</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3514</v>
+        <v>0.8269</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472</v>
+        <v>3.0647</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4659</v>
+        <v>-2.7094</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4091</v>
+        <v>-1.4414</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0568</v>
+        <v>-1.2679</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1846</v>
+        <v>-0.2084</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5217</v>
+        <v>-0.2278</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6629</v>
+        <v>0.0193</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6083</v>
+        <v>0.8197</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6083</v>
+        <v>0.8197</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. CLYBURN</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8289</v>
+        <v>1.1525</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8953</v>
+        <v>1.5621</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0664</v>
+        <v>-0.4096</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1823</v>
+        <v>0.0327</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6145</v>
+        <v>-0.0577</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7968</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8917</v>
+        <v>1.4986</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8269</v>
+        <v>1.3514</v>
       </c>
       <c r="L5" t="n">
-        <v>3.0647</v>
+        <v>0.1472</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7094</v>
+        <v>-1.4659</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4414</v>
+        <v>-1.4091</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2679</v>
+        <v>-0.0568</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.637</v>
+        <v>1.3671</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6563</v>
+        <v>1.0067</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0193</v>
+        <v>0.3605</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8197</v>
+        <v>1.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8197</v>
+        <v>1.6083</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1177</v>
+        <v>-0.0198</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2211</v>
+        <v>1.0566</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1033</v>
+        <v>-1.0764</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5686</v>
+        <v>0.2139</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7359</v>
+        <v>-0.2245</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1673</v>
+        <v>0.4384</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3571</v>
+        <v>2.4047</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2318</v>
+        <v>0.4908</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5889</v>
+        <v>1.9139</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9257</v>
+        <v>-2.1908</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5041</v>
+        <v>-0.7153</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4216</v>
+        <v>-1.4755</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6141</v>
+        <v>-0.2311</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4876</v>
+        <v>-0.3301</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1265</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>-0.9304</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0228</v>
+        <v>-0.4138</v>
       </c>
       <c r="E7" t="n">
-        <v>0.864</v>
+        <v>-0.1761</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8411</v>
+        <v>-0.2378</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2139</v>
+        <v>-0.5686</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2245</v>
+        <v>-0.7359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4384</v>
+        <v>0.1673</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4047</v>
+        <v>0.3571</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4908</v>
+        <v>-0.2318</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9139</v>
+        <v>0.5889</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1908</v>
+        <v>-0.9257</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7153</v>
+        <v>-0.5041</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.4755</v>
+        <v>-0.4216</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1885</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5228</v>
+        <v>0.0905</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3343</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9304</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0586</v>
+        <v>-0.4545</v>
       </c>
       <c r="E8" t="n">
-        <v>0.964</v>
+        <v>1.4672</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0226</v>
+        <v>-1.9217</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0925</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0742</v>
+        <v>0.5298</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1415</v>
+        <v>0.3618</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3558</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.093</v>
+        <v>-1.558</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4023</v>
+        <v>1.7693</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4953</v>
+        <v>-3.3273</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7264</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8474</v>
+        <v>0.3824</v>
       </c>
       <c r="T9" t="n">
-        <v>1.2072</v>
+        <v>0.5742</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3598</v>
+        <v>-0.1918</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1853</v>
+        <v>-4.2861</v>
       </c>
       <c r="E10" t="n">
         <v>-2.8641</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3212</v>
+        <v>-1.422</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9376</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2324</v>
+        <v>-0.3332</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0668</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1656</v>
+        <v>-0.2664</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5599</v>
+        <v>-4.7043</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0861</v>
+        <v>-0.6292</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4738</v>
+        <v>-4.0751</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.7753</v>
+        <v>-4.2864</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.132</v>
+        <v>-2.7072</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6433</v>
+        <v>-1.5792</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.1795</v>
+        <v>-1.377</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.43</v>
+        <v>-1.2765</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.1005</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.5958</v>
+        <v>-2.9094</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7021</v>
+        <v>-1.4306</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8938</v>
+        <v>-1.4787</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7846</v>
+        <v>0.3528</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5149</v>
+        <v>0.1575</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2697</v>
+        <v>0.1953</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.4665</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.604</v>
+        <v>-5.3001</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2937</v>
+        <v>-2.8934</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.3103</v>
+        <v>-2.4066</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.2864</v>
+        <v>-4.7753</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7072</v>
+        <v>-2.132</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5792</v>
+        <v>-2.6433</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.377</v>
+        <v>-1.1795</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2765</v>
+        <v>-0.43</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1005</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.9094</v>
+        <v>-3.5958</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4306</v>
+        <v>-1.7021</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4787</v>
+        <v>-1.8938</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.507</v>
+        <v>-0.3222</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.04</v>
+        <v>-0.2025</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4665</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.409200000000001</v>
+        <v>3.156099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>16.79949999999999</v>
+        <v>17.5463</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.39</v>
+        <v>-14.3902</v>
       </c>
       <c r="G13" t="n">
         <v>-1.946199999999999</v>
@@ -1438,7 +1438,7 @@
         <v>-1.411</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5352000000000003</v>
+        <v>-0.5352000000000006</v>
       </c>
       <c r="J13" t="n">
         <v>22.5385</v>
@@ -1468,13 +1468,13 @@
         <v>15.0771</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5331</v>
+        <v>2.2801</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7289999999999998</v>
+        <v>1.4762</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8039000000000001</v>
+        <v>0.8039999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>2.8223</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0992</v>
+        <v>4.2558</v>
       </c>
       <c r="E14" t="n">
-        <v>5.7659</v>
+        <v>5.53</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6668</v>
+        <v>-1.2742</v>
       </c>
       <c r="G14" t="n">
         <v>2.2871</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6524</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2047</v>
+        <v>-0.0312</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4476</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>J. PUERTO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3391</v>
+        <v>2.7464</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7266</v>
+        <v>2.6232</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3874</v>
+        <v>0.1233</v>
       </c>
       <c r="G15" t="n">
-        <v>2.262</v>
+        <v>1.1287</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1583</v>
+        <v>0.1382</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1036</v>
+        <v>0.9905</v>
       </c>
       <c r="J15" t="n">
-        <v>5.483</v>
+        <v>2.9415</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2719</v>
+        <v>1.5797</v>
       </c>
       <c r="L15" t="n">
-        <v>1.211</v>
+        <v>1.3618</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.221</v>
+        <v>-1.8127</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.1136</v>
+        <v>-1.4414</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1074</v>
+        <v>-0.3713</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.7112</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
         <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3967</v>
+        <v>-0.4698</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2592</v>
+        <v>-0.0863</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6559</v>
+        <v>-0.3835</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2497</v>
+        <v>2.2383</v>
       </c>
       <c r="E16" t="n">
-        <v>5.45</v>
+        <v>2.7266</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2003</v>
+        <v>-0.4883</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7201</v>
+        <v>2.262</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2185</v>
+        <v>2.1583</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4984</v>
+        <v>0.1036</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1009</v>
+        <v>5.483</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8064</v>
+        <v>4.2719</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2944</v>
+        <v>1.211</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3808</v>
+        <v>-3.221</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5879</v>
+        <v>-2.1136</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7929</v>
+        <v>-1.1074</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-3.7112</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5992</v>
+        <v>0.2959</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3645</v>
+        <v>-0.2592</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7653</v>
+        <v>0.5551</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9304</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1444</v>
+        <v>1.214</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.214</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. PUERTO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0108</v>
+        <v>1.9237</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2693</v>
+        <v>4.7423</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2585</v>
+        <v>-2.8185</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1287</v>
+        <v>0.7201</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1382</v>
+        <v>1.2185</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9905</v>
+        <v>-0.4984</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9415</v>
+        <v>3.1009</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5797</v>
+        <v>2.8064</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3618</v>
+        <v>0.2944</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8127</v>
+        <v>-2.3808</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4414</v>
+        <v>-1.5879</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3713</v>
+        <v>-0.7929</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0876</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3195</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2054</v>
+        <v>0.2732</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4402</v>
+        <v>0.6567</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7653</v>
+        <v>-0.3835</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4587</v>
+        <v>0.6832</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1326</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5913</v>
+        <v>0.8158</v>
       </c>
       <c r="G18" t="n">
         <v>0.6459</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1871</v>
+        <v>0.0373</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0378</v>
+        <v>0.1867</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. SESTINA</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1824</v>
+        <v>-0.2248</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0168</v>
+        <v>5.1635</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1992</v>
+        <v>-5.3884</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.162</v>
+        <v>3.0001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.162</v>
+        <v>1.6986</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1.3015</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0168</v>
+        <v>4.9158</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0168</v>
+        <v>2.4031</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.5127</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1788</v>
+        <v>-1.9157</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1788</v>
+        <v>-0.7045</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.2112</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2838</v>
+        <v>-0.168</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.2478</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2838</v>
+        <v>-0.4158</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5361</v>
+        <v>-3.7527</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>-3.7527</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>N. SESTINA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.573</v>
+        <v>-0.3168</v>
       </c>
       <c r="E20" t="n">
-        <v>5.1635</v>
+        <v>0.0168</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.7365</v>
+        <v>-0.3336</v>
       </c>
       <c r="G20" t="n">
-        <v>3.0001</v>
+        <v>-0.162</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6986</v>
+        <v>-0.162</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3015</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>4.9158</v>
+        <v>0.0168</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4031</v>
+        <v>0.0168</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5127</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9157</v>
+        <v>-0.1788</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7045</v>
+        <v>-0.1788</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2112</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5162</v>
+        <v>0.1494</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2478</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7639</v>
+        <v>0.1494</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.7527</v>
+        <v>-0.5361</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.7527</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0597</v>
+        <v>-0.4084</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5067</v>
+        <v>0.7426</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5664</v>
+        <v>-1.151</v>
       </c>
       <c r="G21" t="n">
         <v>1.1179</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4818</v>
+        <v>-0.8305</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3655</v>
+        <v>-0.1296</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1163</v>
+        <v>-0.7009</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8979</v>
+        <v>-1.707</v>
       </c>
       <c r="E22" t="n">
         <v>-0.1877</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7102</v>
+        <v>-1.5194</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9386</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.351</v>
+        <v>-0.1601</v>
       </c>
       <c r="T22" t="n">
         <v>-0.6642</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3132</v>
+        <v>0.5041</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>J. PRADILLA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7582</v>
+        <v>-2.8724</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7353</v>
+        <v>-2.5716</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0229</v>
+        <v>-0.3008</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.9692</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5834</v>
+        <v>-0.0491</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3858</v>
+        <v>-0.4684</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6822</v>
+        <v>2.3778</v>
       </c>
       <c r="K23" t="n">
-        <v>0.175</v>
+        <v>1.2134</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.8572</v>
+        <v>1.1643</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.287</v>
+        <v>-2.8953</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7584</v>
+        <v>-1.2626</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5286</v>
+        <v>-1.6327</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6959</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.3917</v>
+        <v>-4.871</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0905</v>
+        <v>0.8924</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1968</v>
+        <v>-0.0784</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2873</v>
+        <v>0.9709</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. PRADILLA</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2491</v>
+        <v>-3.0156</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9255</v>
+        <v>-2.9712</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3237</v>
+        <v>-0.0444</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-2.9692</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0491</v>
+        <v>-0.5834</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4684</v>
+        <v>-2.3858</v>
       </c>
       <c r="J24" t="n">
-        <v>2.3778</v>
+        <v>-1.6822</v>
       </c>
       <c r="K24" t="n">
-        <v>1.2134</v>
+        <v>0.175</v>
       </c>
       <c r="L24" t="n">
-        <v>1.1643</v>
+        <v>-1.8572</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.8953</v>
+        <v>-1.287</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2626</v>
+        <v>-0.7584</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6327</v>
+        <v>-0.5286</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.2473</v>
+        <v>0.6959</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.871</v>
+        <v>-1.3917</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5157</v>
+        <v>-0.3479</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4323</v>
+        <v>-0.0391</v>
       </c>
       <c r="U24" t="n">
-        <v>0.948</v>
+        <v>-0.3088</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8467</v>
+        <v>-3.3527</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.5277</v>
+        <v>-1.2918</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3189</v>
+        <v>-2.0608</v>
       </c>
       <c r="G25" t="n">
         <v>-3.6282</v>
@@ -2404,13 +2404,13 @@
         <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1489</v>
+        <v>0.3451</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.507</v>
+        <v>-0.2711</v>
       </c>
       <c r="U25" t="n">
-        <v>0.358</v>
+        <v>0.6161</v>
       </c>
       <c r="V25" t="n">
         <v>0.3943</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.4095</v>
+        <v>-0.05029999999999957</v>
       </c>
       <c r="E26" t="n">
-        <v>14.39</v>
+        <v>14.3901</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.7995</v>
+        <v>-14.4403</v>
       </c>
       <c r="G26" t="n">
         <v>1.9462</v>
@@ -2473,7 +2473,7 @@
         <v>-10.8065</v>
       </c>
       <c r="P26" t="n">
-        <v>0.0002000000000002</v>
+        <v>0.0001999999999997559</v>
       </c>
       <c r="Q26" t="n">
         <v>-15.077</v>
@@ -2482,13 +2482,13 @@
         <v>15.0771</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.5331</v>
+        <v>0.8259999999999998</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8039999999999999</v>
+        <v>-0.804</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7294000000000002</v>
+        <v>1.63</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8223</v>
